--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
@@ -834,7 +834,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.32421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.28125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
